--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2025.xlsx
@@ -539,17 +539,17 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Regular price
-                  £10.50</t>
+                  £10.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£10.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -661,24 +661,24 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £12.30</t>
+                  £11.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>£11.99</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£11.99</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>£12.30</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>£12.30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£12.30</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>£12.05</t>
@@ -691,7 +691,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£11.88</t>
+          <t>£13.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -783,24 +783,24 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.50</t>
+                  £15.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>£15.35</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£15.35</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>£15.50</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>£15.50</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£15.50</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>£15.39</t>
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£15.38</t>
+          <t>£16.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.60</t>
+                  £15.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£17.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1027,24 +1027,24 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Regular price
-                  £20.25</t>
+                  £19.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>£19.80</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£19.80</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>£20.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£20.25</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£20.25</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>£19.85</t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£20.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1149,24 +1149,24 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £22.50</t>
+                  £21.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>£21.75</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>£21.75</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>£22.50</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>£22.50</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>£22.50</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>£21.79</t>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£23.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £22.02</t>
+                  £22.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£24.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1393,17 +1393,17 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £25.75</t>
+                  £25.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1515,24 +1515,24 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £28.00</t>
+                  £27.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>£27.30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£27.30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>£28.00</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£28.00</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£28.00</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>£27.34</t>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£27.33</t>
+          <t>£29.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.88</t>
+                  £26.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£29.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1759,24 +1759,24 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Regular price
-                  £36.00</t>
+                  £35.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>£35.55</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>£35.55</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>£36.00</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>£35.57</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>£41.79</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1881,17 +1881,17 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £34.50</t>
+                  £32.95</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2003,17 +2003,17 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>Regular price
-                  £41.00</t>
+                  £40.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2246,17 +2246,17 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.95</t>
+                  £40.92</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.92</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.92</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2587,37 +2587,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>£35.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>£29.80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>£29.50</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>£35.00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>£29.80</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2708,37 +2708,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>£35.90</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£43.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>£35.90</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>£43.00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£36.36</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2829,17 +2829,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>£39.10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>£39.15</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>£39.15</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£39.15</t>
+          <t>£39.10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2950,17 +2950,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>£43.59</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>£43.62</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>£43.62</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£43.62</t>
+          <t>£43.59</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3192,17 +3192,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£43.90</t>
+          <t>£43.85</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£43.90</t>
+          <t>£43.85</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.90</t>
+          <t>£43.85</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3313,17 +3313,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>£992.06</t>
+          <t>£925.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>£992.06</t>
+          <t>£925.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£992.06</t>
+          <t>£925.00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff714081eb5+80197]
-	GetHandleVerifier [0x0x7ff714081f10+80288]
-	(No symbol) [0x0x7ff713e002fa]
-	(No symbol) [0x0x7ff713e57cd7]
-	(No symbol) [0x0x7ff713e57f9c]
-	(No symbol) [0x0x7ff713eaba87]
-	(No symbol) [0x0x7ff713e803bf]
-	(No symbol) [0x0x7ff713ea87fb]
-	(No symbol) [0x0x7ff713e80153]
-	(No symbol) [0x0x7ff713e48b02]
-	(No symbol) [0x0x7ff713e498d3]
-	GetHandleVerifier [0x0x7ff71433e83d+2949837]
-	GetHandleVerifier [0x0x7ff714338c6a+2926330]
-	GetHandleVerifier [0x0x7ff7143586c7+3055959]
-	GetHandleVerifier [0x0x7ff71409cfee+191102]
-	GetHandleVerifier [0x0x7ff7140a50af+224063]
-	GetHandleVerifier [0x0x7ff71408af64+117236]
-	GetHandleVerifier [0x0x7ff71408b119+117673]
-	GetHandleVerifier [0x0x7ff7140710a8+11064]
+	GetHandleVerifier [0x0x7ff699061eb5+80197]
+	GetHandleVerifier [0x0x7ff699061f10+80288]
+	(No symbol) [0x0x7ff698de02fa]
+	(No symbol) [0x0x7ff698e37cd7]
+	(No symbol) [0x0x7ff698e37f9c]
+	(No symbol) [0x0x7ff698e8ba87]
+	(No symbol) [0x0x7ff698e603bf]
+	(No symbol) [0x0x7ff698e887fb]
+	(No symbol) [0x0x7ff698e60153]
+	(No symbol) [0x0x7ff698e28b02]
+	(No symbol) [0x0x7ff698e298d3]
+	GetHandleVerifier [0x0x7ff69931e83d+2949837]
+	GetHandleVerifier [0x0x7ff699318c6a+2926330]
+	GetHandleVerifier [0x0x7ff6993386c7+3055959]
+	GetHandleVerifier [0x0x7ff69907cfee+191102]
+	GetHandleVerifier [0x0x7ff6990850af+224063]
+	GetHandleVerifier [0x0x7ff69906af64+117236]
+	GetHandleVerifier [0x0x7ff69906b119+117673]
+	GetHandleVerifier [0x0x7ff6990510a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2025.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>£10.50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -618,7 +618,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£10.52</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4025-25mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -740,7 +740,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£12.29</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4030-30mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -862,7 +862,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£14.93</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4040-40mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£17.14</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4050-50mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£21.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>£20.47</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4060-60mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£22.34</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4070-70mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£22.52</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4075-75mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>£24.64</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4080-80mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£27.5</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4090-90mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£28.71</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4100-100mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£41.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>£32.97</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4110-110mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>£34.0</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4120-120mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£38.6</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4130-130mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£43.83</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4140-140mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£42.21</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4150-150mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£653.19</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4165-165mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>£861.09</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4200-200mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£29.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4025-38mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2713,32 +2713,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£43.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>£35.90</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>£43.00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£36.36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4040-53mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£39.15</t>
+          <t>£39.10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4050-63mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£43.62</t>
+          <t>£43.59</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£55.49</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4060-73mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>£58.51</t>
+          <t>£49.60</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4050-50mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>£53.49</t>
+          <t>£48.04</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4075-75mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>£55.89</t>
+          <t>£46.50</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff699061eb5+80197]
-	GetHandleVerifier [0x0x7ff699061f10+80288]
-	(No symbol) [0x0x7ff698de02fa]
-	(No symbol) [0x0x7ff698e37cd7]
-	(No symbol) [0x0x7ff698e37f9c]
-	(No symbol) [0x0x7ff698e8ba87]
-	(No symbol) [0x0x7ff698e603bf]
-	(No symbol) [0x0x7ff698e887fb]
-	(No symbol) [0x0x7ff698e60153]
-	(No symbol) [0x0x7ff698e28b02]
-	(No symbol) [0x0x7ff698e298d3]
-	GetHandleVerifier [0x0x7ff69931e83d+2949837]
-	GetHandleVerifier [0x0x7ff699318c6a+2926330]
-	GetHandleVerifier [0x0x7ff6993386c7+3055959]
-	GetHandleVerifier [0x0x7ff69907cfee+191102]
-	GetHandleVerifier [0x0x7ff6990850af+224063]
-	GetHandleVerifier [0x0x7ff69906af64+117236]
-	GetHandleVerifier [0x0x7ff69906b119+117673]
-	GetHandleVerifier [0x0x7ff6990510a8+11064]
+	GetHandleVerifier [0x0x7ff6bc1e1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc1e1f10+80288]
+	(No symbol) [0x0x7ff6bbf602fa]
+	(No symbol) [0x0x7ff6bbfb7cd7]
+	(No symbol) [0x0x7ff6bbfb7f9c]
+	(No symbol) [0x0x7ff6bc00ba87]
+	(No symbol) [0x0x7ff6bbfe03bf]
+	(No symbol) [0x0x7ff6bc0087fb]
+	(No symbol) [0x0x7ff6bbfe0153]
+	(No symbol) [0x0x7ff6bbfa8b02]
+	(No symbol) [0x0x7ff6bbfa98d3]
+	GetHandleVerifier [0x0x7ff6bc49e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc498c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc4b86c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc1fcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc2050af+224063]
+	GetHandleVerifier [0x0x7ff6bc1eaf64+117236]
+	GetHandleVerifier [0x0x7ff6bc1eb119+117673]
+	GetHandleVerifier [0x0x7ff6bc1d10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4100-100mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£1160.0</t>
+          <t>£1248.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-90mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>£1296.0</t>
+          <t>£1328.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-115mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>£1096.66</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-140mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
